--- a/docs/oc-mensuales/adquisicion-de-vehiculos-y-maquinaria/dic-2025.xlsx
+++ b/docs/oc-mensuales/adquisicion-de-vehiculos-y-maquinaria/dic-2025.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>27801.71</v>
+        <v>27442.36</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>42607.59</v>
+        <v>42056.86</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>42607.59</v>
+        <v>42056.86</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>42607.59</v>
+        <v>42056.86</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>42607.59</v>
+        <v>42056.86</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>42607.59</v>
+        <v>42056.86</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>42607.59</v>
+        <v>42056.86</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>42607.59</v>
+        <v>42056.86</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>29460.92</v>
+        <v>29080.12</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>42607.59</v>
+        <v>42056.86</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>37209.85</v>
+        <v>36737.2</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>15587.37</v>
+        <v>15389.38</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>42607.59</v>
+        <v>42066.38</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>42607.59</v>
+        <v>42066.38</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>35642.99</v>
+        <v>35190.25</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>27004.04</v>
+        <v>26661.03</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>25082.71</v>
+        <v>24833.15</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>31425.63</v>
+        <v>31112.96</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>56753.94</v>
+        <v>56189.26</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>66277.28999999999</v>
+        <v>66039.63</v>
       </c>
     </row>
     <row r="22">
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>76733.27</v>
+        <v>76458.12</v>
       </c>
     </row>
     <row r="23">
@@ -1858,7 +1858,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>114363.85</v>
+        <v>113953.77</v>
       </c>
     </row>
     <row r="24">
@@ -1923,7 +1923,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>145686.06</v>
+        <v>145163.66</v>
       </c>
     </row>
     <row r="25">
@@ -1984,7 +1984,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>17522.1</v>
+        <v>17484.18</v>
       </c>
     </row>
     <row r="26">
@@ -2045,7 +2045,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>38249.53</v>
+        <v>38166.75</v>
       </c>
     </row>
     <row r="27">
@@ -2106,7 +2106,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>75738.24000000001</v>
+        <v>75574.33</v>
       </c>
     </row>
     <row r="28">
@@ -2171,7 +2171,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>154308.04</v>
+        <v>153974.09</v>
       </c>
     </row>
     <row r="29">
@@ -2232,7 +2232,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>75905.71000000001</v>
+        <v>75741.44</v>
       </c>
     </row>
     <row r="30">
@@ -2297,7 +2297,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>246210.53</v>
+        <v>245677.7</v>
       </c>
     </row>
     <row r="31">
@@ -2362,7 +2362,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>146476.45</v>
+        <v>146159.45</v>
       </c>
     </row>
     <row r="32">
@@ -2423,7 +2423,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>72905.19</v>
+        <v>72747.41</v>
       </c>
     </row>
     <row r="33">
@@ -2484,7 +2484,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>47201.86</v>
+        <v>47099.71</v>
       </c>
     </row>
     <row r="34">
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>49950.28</v>
+        <v>49842.18</v>
       </c>
     </row>
     <row r="35">
@@ -2610,7 +2610,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>63091.25</v>
+        <v>62361.09</v>
       </c>
     </row>
     <row r="36">
@@ -2675,7 +2675,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>169795.78</v>
+        <v>167830.71</v>
       </c>
     </row>
     <row r="37">
@@ -2736,7 +2736,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>21030.42</v>
+        <v>20787.03</v>
       </c>
     </row>
     <row r="38">
@@ -2797,7 +2797,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>20619.69</v>
+        <v>20381.06</v>
       </c>
     </row>
     <row r="39">
@@ -2858,7 +2858,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>17522.1</v>
+        <v>17319.32</v>
       </c>
     </row>
     <row r="40">
@@ -2919,7 +2919,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>37396.5</v>
+        <v>36963.71</v>
       </c>
     </row>
     <row r="41">
@@ -2980,7 +2980,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>26174.04</v>
+        <v>25952.33</v>
       </c>
     </row>
     <row r="42">
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>26196.21</v>
+        <v>25974.31</v>
       </c>
     </row>
     <row r="43">
@@ -3102,7 +3102,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>26407.84</v>
+        <v>26184.15</v>
       </c>
     </row>
     <row r="44">
@@ -3163,7 +3163,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>59359.52</v>
+        <v>58856.7</v>
       </c>
     </row>
     <row r="45">
@@ -3224,7 +3224,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>42289.44</v>
+        <v>41931.21</v>
       </c>
     </row>
     <row r="46">
@@ -3285,7 +3285,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>21007.82</v>
+        <v>20829.86</v>
       </c>
     </row>
     <row r="47">
@@ -3346,7 +3346,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>25082.71</v>
+        <v>24870.24</v>
       </c>
     </row>
     <row r="48">
@@ -3407,7 +3407,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>54008.07</v>
+        <v>53550.58</v>
       </c>
     </row>
     <row r="49">
@@ -3468,7 +3468,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>29778.33</v>
+        <v>29754.39</v>
       </c>
     </row>
     <row r="50">
@@ -3529,7 +3529,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>20596.44</v>
+        <v>20579.89</v>
       </c>
     </row>
     <row r="51">
@@ -3594,7 +3594,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>85921.94</v>
+        <v>86251.73</v>
       </c>
     </row>
     <row r="52">
@@ -3655,7 +3655,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>73205.75</v>
+        <v>73486.73</v>
       </c>
     </row>
     <row r="53">
@@ -3716,7 +3716,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>11090.82</v>
+        <v>11133.39</v>
       </c>
     </row>
     <row r="54">
@@ -3777,7 +3777,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>21497.76</v>
+        <v>21580.27</v>
       </c>
     </row>
     <row r="55">
@@ -3838,7 +3838,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>68954.47</v>
+        <v>69219.13</v>
       </c>
     </row>
     <row r="56">
@@ -3903,7 +3903,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>580067.77</v>
+        <v>582696.4300000001</v>
       </c>
     </row>
     <row r="57">
@@ -3968,7 +3968,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>290657.08</v>
+        <v>291974.24</v>
       </c>
     </row>
     <row r="58">
@@ -4029,7 +4029,7 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>78845.03999999999</v>
+        <v>79202.33</v>
       </c>
     </row>
     <row r="59">
@@ -4090,7 +4090,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>25527.77</v>
+        <v>25643.45</v>
       </c>
     </row>
     <row r="60">
@@ -4151,7 +4151,7 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>59595.92</v>
+        <v>59865.99</v>
       </c>
     </row>
     <row r="61">
@@ -4212,7 +4212,7 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>37677.46</v>
+        <v>37777.37</v>
       </c>
     </row>
     <row r="62">
@@ -4273,7 +4273,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>19069.53</v>
+        <v>19120.1</v>
       </c>
     </row>
     <row r="63">
@@ -4338,7 +4338,7 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>93814.64</v>
+        <v>94063.41</v>
       </c>
     </row>
     <row r="64">
@@ -4399,7 +4399,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>25472.64</v>
+        <v>25540.19</v>
       </c>
     </row>
     <row r="65">
@@ -4460,7 +4460,7 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>29679.76</v>
+        <v>29638.13</v>
       </c>
     </row>
     <row r="66">
@@ -4521,7 +4521,7 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>16478.4</v>
+        <v>16455.28</v>
       </c>
     </row>
     <row r="67">
@@ -4582,7 +4582,7 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>21497.76</v>
+        <v>21467.6</v>
       </c>
     </row>
     <row r="68">
@@ -4647,7 +4647,7 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>279545.37</v>
+        <v>279903.74</v>
       </c>
     </row>
     <row r="69">
@@ -4708,7 +4708,7 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>24463.31</v>
+        <v>24494.68</v>
       </c>
     </row>
     <row r="70">
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>44619.31</v>
+        <v>44676.51</v>
       </c>
     </row>
     <row r="71">
@@ -4830,7 +4830,7 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>54014.19</v>
+        <v>54083.43</v>
       </c>
     </row>
     <row r="72">
@@ -4891,7 +4891,7 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>59362.12</v>
+        <v>59770.72</v>
       </c>
     </row>
     <row r="73">
@@ -4952,7 +4952,7 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>26566.96</v>
+        <v>26749.82</v>
       </c>
     </row>
     <row r="74">
@@ -5013,7 +5013,7 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>18107.51</v>
+        <v>18232.15</v>
       </c>
     </row>
     <row r="75">
@@ -5074,7 +5074,7 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>30316.22</v>
+        <v>30524.89</v>
       </c>
     </row>
     <row r="76">
@@ -5135,7 +5135,7 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>31786.1</v>
+        <v>32004.89</v>
       </c>
     </row>
     <row r="77">
@@ -5196,7 +5196,7 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>35642.99</v>
+        <v>35888.33</v>
       </c>
     </row>
     <row r="78">
@@ -5257,7 +5257,7 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>32867.41</v>
+        <v>33093.64</v>
       </c>
     </row>
     <row r="79">
@@ -5318,7 +5318,7 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>37396.5</v>
+        <v>37653.91</v>
       </c>
     </row>
     <row r="80">
@@ -5383,7 +5383,7 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>109847.59</v>
+        <v>110786.33</v>
       </c>
     </row>
     <row r="81">
@@ -5444,7 +5444,7 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>10503.91</v>
+        <v>10616.58</v>
       </c>
     </row>
     <row r="82">
@@ -5505,7 +5505,7 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>37396.5</v>
+        <v>37797.64</v>
       </c>
     </row>
     <row r="83">
@@ -5570,7 +5570,7 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>148074.09</v>
+        <v>148883.86</v>
       </c>
     </row>
     <row r="84">
@@ -5631,7 +5631,7 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>65077.46</v>
+        <v>65433.35</v>
       </c>
     </row>
     <row r="85">
@@ -5692,7 +5692,7 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>37677.46</v>
+        <v>37883.5</v>
       </c>
     </row>
     <row r="86">
@@ -5757,7 +5757,7 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>94856.52</v>
+        <v>95375.27</v>
       </c>
     </row>
     <row r="87">
@@ -5818,7 +5818,7 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>37396.5</v>
+        <v>37601.01</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-mensuales/adquisicion-de-vehiculos-y-maquinaria/dic-2025.xlsx
+++ b/docs/oc-mensuales/adquisicion-de-vehiculos-y-maquinaria/dic-2025.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC dic-2025" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC dic-2025" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -671,7 +671,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1784,7 +1784,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -1834,7 +1834,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1849,7 +1849,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -1964,7 +1964,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2162,7 +2162,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2353,7 +2353,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -3570,7 +3570,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3585,7 +3585,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -3894,7 +3894,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -3959,7 +3959,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -4192,7 +4192,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -4253,7 +4253,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -4329,7 +4329,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -4638,7 +4638,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -5374,7 +5374,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -5561,7 +5561,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -5672,7 +5672,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -5748,7 +5748,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">

--- a/docs/oc-mensuales/adquisicion-de-vehiculos-y-maquinaria/dic-2025.xlsx
+++ b/docs/oc-mensuales/adquisicion-de-vehiculos-y-maquinaria/dic-2025.xlsx
@@ -1032,7 +1032,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Chillan Viejo</t>
+          <t>ILUSTRE MUNICIPALIDAD DE CHILLAN VIEJO</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE CUREPTO</t>
+          <t>Ilustre Municipalidad de Curepto</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -2343,7 +2343,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>INCHCAPE CAMIONES Y BUSES CHILE S.A.</t>
+          <t>Inchcape Camiones y Buses Chile S.A.</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2469,7 +2469,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>COMERCIAL MOTORES DE LOS ANDES SPA</t>
+          <t>Comercial Motores de los Andes SpA</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2960,7 +2960,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3087,7 +3087,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>COMERCIAL MOTORES DE LOS ANDES SPA</t>
+          <t>Comercial Motores de los Andes SpA</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3575,7 +3575,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Tattersall Maquinarias S.A.</t>
+          <t>TATTERSALL MAQUINARIAS S.A.</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -4070,7 +4070,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -4384,7 +4384,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>COMERCIAL MOTORES DE LOS ANDES SPA</t>
+          <t>Comercial Motores de los Andes SpA</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -4754,7 +4754,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>INCHCAPE CAMIONES Y BUSES CHILE S.A.</t>
+          <t>Inchcape Camiones y Buses Chile S.A.</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -4805,7 +4805,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Chillan Viejo</t>
+          <t>ILUSTRE MUNICIPALIDAD DE CHILLAN VIEJO</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -4876,7 +4876,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>INCHCAPE CAMIONES Y BUSES CHILE S.A.</t>
+          <t>Inchcape Camiones y Buses Chile S.A.</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -5232,7 +5232,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Division de Bienestar Social</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -5551,7 +5551,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>INCHCAPE CAMIONES Y BUSES CHILE S.A.</t>
+          <t>Inchcape Camiones y Buses Chile S.A.</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">

--- a/docs/oc-mensuales/adquisicion-de-vehiculos-y-maquinaria/dic-2025.xlsx
+++ b/docs/oc-mensuales/adquisicion-de-vehiculos-y-maquinaria/dic-2025.xlsx
@@ -562,7 +562,11 @@
           <t>79.649.970-2</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +692,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +757,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +822,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +887,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +952,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1017,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1082,11 @@
           <t>96.928.530-4</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1147,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1334,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1399,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1416,7 +1464,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1477,7 +1529,11 @@
           <t>80.522.900-4</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1599,7 +1655,11 @@
           <t>79.649.970-2</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1721,7 +1781,11 @@
           <t>96.889.440-4</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1977,7 +2041,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2038,7 +2106,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2099,7 +2171,11 @@
           <t>96.572.360-9</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2225,7 +2301,11 @@
           <t>96.572.360-9</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2416,7 +2496,11 @@
           <t>96.572.360-9</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2477,7 +2561,11 @@
           <t>76.005.909-9</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2603,7 +2691,11 @@
           <t>96.928.530-4</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2729,7 +2821,11 @@
           <t>96.928.530-4</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2790,7 +2886,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2851,7 +2951,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2912,7 +3016,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2973,7 +3081,11 @@
           <t>76.296.863-0</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3034,7 +3146,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3095,7 +3211,11 @@
           <t>76.005.909-9</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3156,7 +3276,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3217,7 +3341,11 @@
           <t>81.318.700-0</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3400,7 +3528,11 @@
           <t>80.522.900-4</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3461,7 +3593,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3522,7 +3658,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3648,7 +3788,11 @@
           <t>91.502.000-3</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3709,7 +3853,11 @@
           <t>81.318.700-0</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3770,7 +3918,11 @@
           <t>91.502.000-3</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3831,7 +3983,11 @@
           <t>96.572.360-9</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4022,7 +4178,11 @@
           <t>79.853.470-K</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4083,7 +4243,11 @@
           <t>76.296.863-0</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4144,7 +4308,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4392,7 +4560,11 @@
           <t>76.005.909-9</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4453,7 +4625,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4514,7 +4690,11 @@
           <t>79.649.970-2</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4575,7 +4755,11 @@
           <t>91.502.000-3</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4701,7 +4885,11 @@
           <t>81.318.700-0</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4762,7 +4950,11 @@
           <t>76.141.853-k</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4823,7 +5015,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4884,7 +5080,11 @@
           <t>76.141.853-k</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L72" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5006,7 +5206,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5067,7 +5271,11 @@
           <t>80.522.900-4</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5128,7 +5336,11 @@
           <t>79.649.970-2</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5189,7 +5401,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5250,7 +5466,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L78" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5311,7 +5531,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L79" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5498,7 +5722,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L82" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5624,7 +5852,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L84" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5811,7 +6043,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L87" t="inlineStr">
         <is>
           <t>USD</t>
